--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260909.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260909.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>138,025</t>
+          <t>137,725</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>26.73%</t>
+          <t>26.53%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>99,990</t>
+          <t>99,790</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.54%</t>
+          <t>8.53%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.01%</t>
+          <t>7.89%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>50,865</t>
+          <t>50,765</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>6.03%</t>
+          <t>6.31%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>121,305</t>
+          <t>121,005</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.35%</t>
+          <t>5.29%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>59,650</t>
+          <t>59,550</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.21%</t>
+          <t>4.13%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.14%</t>
+          <t>3.16%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>19,825</t>
+          <t>19,725</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.12%</t>
+          <t>3.07%</t>
         </is>
       </c>
     </row>
@@ -787,56 +787,56 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>65,495</t>
+          <t>65,295</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>3.05%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>DUK US</t>
+          <t>NET US</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>杜克能源公司</t>
+          <t>Cloudflare公司</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>45,295</t>
+          <t>18,283</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.89%</t>
+          <t>3.04%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>NET US</t>
+          <t>DUK US</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Cloudflare公司</t>
+          <t>杜克能源公司</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>18,383</t>
+          <t>45,195</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.75%</t>
+          <t>2.88%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>2.39%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.77%</t>
+          <t>1.75%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.56%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.50%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.48%</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>36,050</t>
+          <t>35,950</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.45%</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>59,198</t>
+          <t>59,098</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1041,39 +1041,39 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>ED US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>聯合愛迪生</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>21,308</t>
+          <t>7,890</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.25%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>ED US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>聯合愛迪生</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>7,990</t>
+          <t>21,308</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,22 +1085,22 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>64,480,456</t>
+          <t>18,355</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
@@ -1122,73 +1122,73 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>0.98%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>18,355</t>
+          <t>125,985</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>125,985</t>
+          <t>15,871</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>0.89%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>15,871</t>
+          <t>51,016,112</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.78%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.74%</t>
+          <t>0.72%</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>386,617</t>
+          <t>444,323</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.23%</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>23,655</t>
+          <t>335,499</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
